--- a/AAII_Financials/Quarterly/COTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>COTY</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1269200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1281600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1678600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1577200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1252400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1299100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1669900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1671500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1363400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1385600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1727600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1641400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1351600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1288900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1523600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1390000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1168300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1186200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1578200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1371700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1062400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1027800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1415600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1124100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>560400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1062500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1683700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1411200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1506200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4781700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2511200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2031300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2299400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2222700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2637600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2238300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2241300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2032100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2296700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1080200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>496500</v>
+      </c>
+      <c r="E9" s="3">
         <v>489700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>608000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>560400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>472700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>466700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>554400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>576900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>488000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>487800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>603500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>599500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>502100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>478100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>525300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>501300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>446200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>423100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>561100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>504800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>415900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>388600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>584000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>464900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>332900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1055500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1491600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1300300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1393100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2637100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>952100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>803900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>882800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>795900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1014800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>863800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>870200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>808000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>889100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>889400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>772700</v>
+      </c>
+      <c r="E10" s="3">
         <v>791900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1070600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1016800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>779700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>832400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1115500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1094600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>875400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>897800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1124100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1041900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>849500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>810800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>998300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>888700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>722100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>763100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1017100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>866900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>646500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>639200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>831600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>659200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>227500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>192100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>110900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>113100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2144600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1559100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1227400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1416600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1426800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1622800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1374500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1371100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1224100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1407600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>190800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,13 +1248,14 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>121200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1249,11 +1263,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>123000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1261,11 +1275,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>126800</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1273,11 +1287,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>105200</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E14" s="3">
         <v>363300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>216200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2700</v>
       </c>
-      <c r="G14" s="3">
-        <v>-183500</v>
-      </c>
       <c r="H14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I14" s="3">
         <v>289400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>34700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-9000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-17400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>18900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-3200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>18100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-19200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>34800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>113000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>81700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>546500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>85200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>206100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-56900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2809200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1111300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1038400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>69000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>181600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>117700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>90500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>142300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>669900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>298200</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>212700</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E15" s="3">
         <v>74500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>74100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>39300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>45600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>45900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>47300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>48100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>48000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>48500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>48300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>48600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>48700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>48200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>47600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>47300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>48800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>50200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>51400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>57000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>61800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>62200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>61800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>65400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>62500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>61600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>50800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>58300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>59400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>187300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>88500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>92500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>92200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>92800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>89600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>78200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>56100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>102600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>95200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1289600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1516100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1390500</v>
       </c>
-      <c r="G17" s="3">
-        <v>1251300</v>
-      </c>
       <c r="H17" s="3">
+        <v>1224100</v>
+      </c>
+      <c r="I17" s="3">
         <v>1289400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1399000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1433400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1320400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1310200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1487500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1417300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1219500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1247800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1324300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1218100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1245700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1129100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1334200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1354500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1060600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1029200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1398600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1190100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1480900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1362000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1764200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1347200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4250600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5725700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3315800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2052000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2371900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2202800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2463200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2209600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2520300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2224600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2310800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1033800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>162500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>186700</v>
       </c>
-      <c r="G18" s="3">
-        <v>1100</v>
-      </c>
       <c r="H18" s="3">
+        <v>28300</v>
+      </c>
+      <c r="I18" s="3">
         <v>9700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>270900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>238100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>75400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>240100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>224100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>132100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>41100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>199300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>171900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-77400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>57100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>244000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-920500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-299500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-80500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>64000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2744400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-944000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-804600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-20700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-72500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>19900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>174400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>28700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-279000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-192500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-14100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E20" s="3">
         <v>52700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>67700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>29400</v>
       </c>
-      <c r="G20" s="3">
-        <v>203800</v>
-      </c>
       <c r="H20" s="3">
+        <v>48100</v>
+      </c>
+      <c r="I20" s="3">
         <v>134900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>126600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>48600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>93800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>20900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-66100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>88100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-161500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>145900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>89900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-147600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>58600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>127000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>389100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>63900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-41800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>16300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-117300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>3300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E21" s="3">
         <v>13800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>168900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>196600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-157100</v>
-      </c>
       <c r="H21" s="3">
+        <v>25800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-79300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>191600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>237600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>103000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>354500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>184600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>180600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>250800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>449000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>368400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-98100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>237600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>500800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>544100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>141200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>208900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>144300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>82900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-793500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-114500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>91400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>239000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2542400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-511000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-621500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>170500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>102000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>212800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>362100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>194700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-138000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-9200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>159600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E22" s="3">
         <v>39600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>52400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>51600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>50200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>56700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>60400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>64300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>58800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>61700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>66800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>73300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>65200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>65000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>57600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>55800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>60900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>61700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>62800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>60500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>51700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>60600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59000</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>58700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>53600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>61200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>79200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>76800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>74100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>72400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>74600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>75500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>69600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>67400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>61700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>59000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>59200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-89800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-458900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-168600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>107100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-73500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-460600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>56600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>132700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-107400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>257400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>51100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>78800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>141600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>280200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>204200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-280800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>54800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>309300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>343500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-68500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-59800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-122300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-962300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-363600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-140300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2807300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1138100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-877700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-87500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-166100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-55700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>110700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-41400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-339900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-252800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-70000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-53200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-52400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-58400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>42000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>71400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>43300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>38800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>69700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>49400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>114600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>132900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-244900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-260700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-24200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-30600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>78300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-77400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-21900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-10600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-7900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-25300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-38900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-122100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-405700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-116200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>74000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-69300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-402200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>90700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-95600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>186000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>241400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>134500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-281100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>54300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>259900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>228900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-201400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>30000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>122600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-701600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-303800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-101300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2783100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1107500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-956000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-144200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-45100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>118600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-16100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-301000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-159400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>52100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-144300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-411400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-126900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>64600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-72100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-409000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>79600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>177600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>105100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>235000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>125300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-286000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>188900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>103000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-221100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-39800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>95900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-696200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-311000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-106000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2783000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-960600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-155300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-62000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>109200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-304800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-164200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>46800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,71 +3255,71 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>1200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>3800</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>10900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-235600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>104700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-76600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>203200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>84900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>39500</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>137400</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-26000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
+      <c r="AL29" s="3">
+        <v>0</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-52700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-67700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-29400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-203800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-134900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-126600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-48600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-93800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-20900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>66100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-88100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>161500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-145900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-89900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>147600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-58600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-127000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-389100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-63900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>16200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>41800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>117300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-408100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-123600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>67900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-68800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-405700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>82900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-96900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>180900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>108400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>235000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>125300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-284800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>50300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>192700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>103000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-210200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-275400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>200600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-772800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-107800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-21100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>52300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2799400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-984800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-960600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-181300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-77000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>109200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-304800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-164200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>46800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-408100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-123600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>67900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-68800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-405700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>82900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-96900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>180900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>108400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>235000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>125300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-284800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>50300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>192700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>103000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-210200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-275400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>200600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-772800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-107800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-21100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>52300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2799400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-984800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-960600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-181300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-77000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>109200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-304800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-164200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>46800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>176100</v>
+      </c>
+      <c r="E41" s="3">
         <v>257100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>436700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>264600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>257100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>243500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>249600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>283600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>260200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>450000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>280000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>246900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>245000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>280800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>215700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>233300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>668600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>523400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>376900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>253500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>315300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>549100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>535700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>308300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1278500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>288800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>350400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>340400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>384100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>417500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>423300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>331600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>460800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>400100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>919200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>535400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>767000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>939200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4380,11 +4470,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>2800</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4463,257 +4553,266 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>525800</v>
+      </c>
+      <c r="E43" s="3">
         <v>565200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>689400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>796600</v>
       </c>
-      <c r="G43" s="3">
-        <v>663800</v>
-      </c>
       <c r="H43" s="3">
+        <v>526400</v>
+      </c>
+      <c r="I43" s="3">
         <v>605300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>621000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>747000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>642400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>533000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>602900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>613300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>612500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>464200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>433800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>483000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>364600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>479200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>506800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>517800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>348000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>398100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>531700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>521700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>440100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>844200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1110000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1036600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>858900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1211600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1542700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1484400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1536000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1555400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1743900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1609500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1470300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1380900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1450300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>768500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>838700</v>
+      </c>
+      <c r="E44" s="3">
         <v>786300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>778200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>807500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>794500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>717300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>705800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>782500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>764100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>759700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>775500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>845400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>853400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>798100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>718200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>676400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>661500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>643100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>589000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>660700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>650800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>604700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>626100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>727700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>678200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>959900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1015800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1150800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>860100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1183500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1164600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1251200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1148900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1258500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1155300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1172000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1052600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1034300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1014800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>616700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>280700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4721,11 +4820,11 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>126200</v>
-      </c>
-      <c r="H45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="H45" s="3">
+        <v>263600</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -4733,11 +4832,11 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>142000</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
@@ -4745,285 +4844,291 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>193000</v>
       </c>
-      <c r="P45" s="3" t="s">
+      <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>473500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>454900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>422500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>413300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>559200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>504800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>530800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>500100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>510600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5191100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5068400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>590500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>608700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>594900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1211400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>623300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>589600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>581100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>634500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>635900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>579900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>548800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>523200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>564000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>505000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>344500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1917700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1935500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2245400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2173700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1953300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1930100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1952500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2233700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1963500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1985600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2421600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2243500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2051700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1914500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1906300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1830000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1681900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2204200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2178400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2060200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1783100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1818200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2217500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6976200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6495000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3673100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3023300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3132700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3270800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3402500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3714400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3740000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3651000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3910600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3879200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4249500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3581500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3746200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3909300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2107700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>58000</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1003000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1002000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1000000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1056700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1089600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1090600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1086500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1084200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1072100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1068900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1049800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1050600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>976700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>842600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1038900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1189800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1665600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1276200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1266800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1186500</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
@@ -5040,8 +5145,8 @@
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>876900</v>
+      </c>
+      <c r="E48" s="3">
         <v>872700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>913000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>932700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>974900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>936800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>912700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>980200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>974200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>973900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>995700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>970600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>999600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>986800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>990200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>968200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1036400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1091700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1072300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1149700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1236600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1274000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1356100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1386600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1453000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1833000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1967400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1961800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1332700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1609200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1625700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1648000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1680800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1689200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1647300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1633800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1632100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1555800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1418700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>665700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6585300</v>
+      </c>
+      <c r="E49" s="3">
         <v>6670600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7173600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7249800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7277000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7002500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7234800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7596200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7471300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7597700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7761400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7615900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7785900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7827500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7768300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7511000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7817500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8164400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8212800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8373400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8581100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8501500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8645600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8447200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8346000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>12364300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>12008500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11881100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8698100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>15410100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>15594400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>16788600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>16891500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>17634900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>17415600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>17231900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>16980700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>17080600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16206700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4230300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E52" s="3">
         <v>140700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>184000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>138300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>138900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>105300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>92100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>103900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>92100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>97600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>155300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>143600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>165600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>288700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>739200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>662000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>737700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>769900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>780700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>789500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>814400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>761800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>754100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>970100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>434800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>439600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>361700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>307900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4408400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>334800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>336200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>416100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>406900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>530300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>503500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>457900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>353900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>390700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>356300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>189700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10200400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10228900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11077100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12058500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11907700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11470500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11724300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12516000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12082500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12322200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13015700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12616900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12661600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12705500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12454600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11947900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12116100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13269100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13434000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14038400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13691400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13622300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14159800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17780100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16728800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18310000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17360900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17283500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17710000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20756600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>21270700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22592700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22630200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23765000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23445600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>23573100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>22548200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>22773300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>21891000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>7193400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1768200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2120500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1900900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1890000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1279800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1364600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1323300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1997600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1250100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1462900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1375400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1444700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1407700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1489700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1229700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1268300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1280500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1394300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1232500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1166100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1051800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1154300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1086300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1190300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1422100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1574800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1548100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1583500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1844000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1818900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1794900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1928600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1709300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1758600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1768300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1732100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1456500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1401000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>964600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E58" s="3">
         <v>65800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>68000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>70600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>60800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>63200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>70400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>100700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>146500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>129400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>68100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>516500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>23800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>418200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>24200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>193700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>201200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>195400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>188300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>185900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>188000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>185400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>193800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>196700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>255700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>200700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>218900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>231600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>295900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>223300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>209100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>193000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>186700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>156600</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E59" s="3">
         <v>521900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>651600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>579200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>468800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>69300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>354700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>124000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>126200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>492400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>171400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1357800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1348200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1274300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1399200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1484000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1421100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1225100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1320400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1627600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2396300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2207100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1477800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1750800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1503900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1697900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1538100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1790400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1795500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1896500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2000900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2101300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1956900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1862400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1608200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1550100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>761700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2540500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2356300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2839800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2546800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2538300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2359600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2746200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2637600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2601800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2476200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2851000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2828100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2736800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2757300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2915600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2610600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2565600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3196200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2902100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3071800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2415400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2565900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2983100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3678000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3585700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3085800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3513600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3237400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3475200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3578800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3791100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4044000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3941800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4155800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3948500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3803600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3257700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3137800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1882900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3216300</v>
+      </c>
+      <c r="E61" s="3">
         <v>3359200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3196400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4230900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4177300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4020900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3590300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4158300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4060500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4134900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3934500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4339700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4426500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4480500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4156400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4455200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4551500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4459300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5020900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5703700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6437300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6218700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6142100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9113800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8607900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9172000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7233800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7453500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7469900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7490900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7560900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7789700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7305400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7628600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7145800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7541900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6928300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6909300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6308400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4210400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>425600</v>
+      </c>
+      <c r="E62" s="3">
         <v>444900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>432200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>472700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>485100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>384300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>336100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>379100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>347400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>328000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>343100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>343500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>324600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>295200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1591300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1569700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1583400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1748800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1758700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1735300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1692400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1579800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1659800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1479600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1227300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1992400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2033300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2033700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1719700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1732200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1745900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1776600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1764300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2029600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2077200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2066500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1947500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2469300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2563700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>763700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6821300</v>
+      </c>
+      <c r="E66" s="3">
         <v>6727200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7132400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8003000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7952100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7551000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7509900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8042900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7834800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7903800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8158400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8467200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8428300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8569000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8923200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8896100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8961600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9670400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9962500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10795000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10830700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10660100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11082400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14579000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13724200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14577800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12889200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12828500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13123100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13258900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13665600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13985200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13780500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14265700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14016500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>14120800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13233500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13163600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12097900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6942400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7568,7 +7736,7 @@
         <v>142400</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>142400</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -7604,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>100</v>
@@ -7616,7 +7784,7 @@
         <v>100</v>
       </c>
       <c r="AG70" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH70" s="3">
         <v>0</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5878200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5737200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5325900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5198500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5266400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5197600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4791900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4815600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4898500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4801600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4805400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4986300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4987900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5020800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5129200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5367500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5496100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5214600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5268200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5529600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5755600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5569600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5585200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5332900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5548600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4782300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4510700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-4489600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4541200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1741800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1729700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-769100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-626200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-438400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-361400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-470600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-459200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-154400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-37000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2989700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3091400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3526900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3643400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3542700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3495000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3784700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4045200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3827100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3992600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4424800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3721300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3811100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3737600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3531400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3051800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3154500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3598700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3471500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3243400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2860700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2962200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3077400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3201100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3004600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3732200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4471600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4454900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4586800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7497600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7605100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8607500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8849700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9499300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9429100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9452300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9314700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9609700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>9793100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>251000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-408100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-123600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>67900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-68800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-405700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>82900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-96900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>180900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>108400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>235000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>125300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-284800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>50300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>192700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>103000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-210200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-275400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>200600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-772800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-107800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-21100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>52300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2799400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-984800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-960600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-181300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-77000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>109200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-304800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-164200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>46800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E83" s="3">
         <v>59200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>58300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>56500</v>
       </c>
       <c r="G83" s="3">
         <v>56500</v>
       </c>
       <c r="H83" s="3">
+        <v>56500</v>
+      </c>
+      <c r="I83" s="3">
         <v>55900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>57100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>60200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>59200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>56200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>59300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>78100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>103800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>106600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>126900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>121900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>129800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>137800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>149200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>146400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>143500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>146200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>168800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>190400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>178100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>179200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>185700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>550300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>182100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>185600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>193500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>193000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>181800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>168700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>140200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>184600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>170400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-203100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>559700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>65200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>83200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-122500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>464500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>67400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>176500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-170000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>421900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>186200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>104900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-124600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>482200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>163200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-32900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>24800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>449000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>285700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-186300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>430100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>42600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-255400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-257500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>422100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>39900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>188200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>451400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>319600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-81900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>224800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-118900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>316700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-8900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>50800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>43300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>678400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-15000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-45600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-54000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-48300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-45900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-45500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-75300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-64300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-58900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-66800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-53900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-75000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-47000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-41000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-30200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-70900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-86400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-95700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-330900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-125700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-133600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-86500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-120800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-111400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-108300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-125800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-173600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-74100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-45600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>712500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-53800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-48300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>28100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-77300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-42100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>29800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-75000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>206900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>119500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-45000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-30200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>2795600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-81500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-653400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-58600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-60800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-83000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-371000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-125700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-174400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-106900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-116000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-714100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-255200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-86800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10236,29 +10470,29 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>100</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>100</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>200</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>8</v>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10291,49 +10525,49 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-66500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-67100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-63300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-63400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-282800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-94600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-93800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-93900</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-93800</v>
       </c>
       <c r="AK96" s="3">
         <v>-93800</v>
       </c>
       <c r="AL96" s="3">
+        <v>-93800</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-94300</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-93400</v>
       </c>
       <c r="AN96" s="3">
         <v>-93400</v>
@@ -10342,10 +10576,13 @@
         <v>-93400</v>
       </c>
       <c r="AP96" s="3">
+        <v>-93400</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-92400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-125200</v>
+      </c>
+      <c r="E100" s="3">
         <v>70500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1098900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-42700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>77200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-450900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-72600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-207300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-78600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-71700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>139000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-448800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-87800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-391300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-95200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-424800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-122700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-52700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>190400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3197000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>264200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-652500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1910500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-417400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>36700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-143600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-198100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>351800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-221600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>257700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-459200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>492400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-185900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>481900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>167800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E101" s="3">
         <v>8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-21600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-13100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>12000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-14800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-20600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>8700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>6400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>21300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>16700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-29800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-177800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>174900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-197300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>165800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>33900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>61200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-436400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>137700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>140100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>112000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-47600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-247300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>30000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>223300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-959600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>972100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-41900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-39800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>58000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>91000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-124300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>60800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-518900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>373900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-221300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-172200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>561200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>30600</v>
       </c>
     </row>
